--- a/output/pdf_financials_xlsx/OVT.xlsx
+++ b/output/pdf_financials_xlsx/OVT.xlsx
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.153905</v>
+        <v>0.162316</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.288545</v>
+        <v>0.293645</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -963,22 +963,22 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000449</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.005153</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.011704</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.00233</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>9.6e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1798,7 +1798,7 @@
         <v>-0.183279</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.192865</v>
+        <v>-0.193314</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>-0.183279</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.192865</v>
+        <v>-0.193314</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -2161,10 +2161,10 @@
         <v>0.156574</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.011718</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.009409000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2255,10 +2255,10 @@
         <v>0.156574</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.011718</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.009409000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2819,10 +2819,10 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.027822</v>
+        <v>0.016104</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.022786</v>
+        <v>0.013377</v>
       </c>
     </row>
     <row r="49">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -15472,7 +15472,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -15492,13 +15492,13 @@
         </is>
       </c>
       <c r="I107" s="5" t="n">
-        <v>-0.230699</v>
+        <v>0.230699</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>-0.183279</v>
+        <v>0.183279</v>
       </c>
       <c r="K107" s="5" t="n">
-        <v>-0.196621</v>
+        <v>0.196621</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">

--- a/output/pdf_financials_xlsx/OVT.xlsx
+++ b/output/pdf_financials_xlsx/OVT.xlsx
@@ -5548,10 +5548,10 @@
         <v>0</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>0.007594</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>0.002857</v>
       </c>
       <c r="L103" s="3" t="n">
         <v>0</v>
@@ -5719,10 +5719,10 @@
         <v>0</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>0.007594</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>0.002857</v>
       </c>
       <c r="L106" s="3" t="n">
         <v>0</v>
@@ -11974,7 +11974,11 @@
           <t>Decrease in prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
